--- a/output/xlsx/PesquisarExtracao--GT-.xlsx
+++ b/output/xlsx/PesquisarExtracao--GT-.xlsx
@@ -92,7 +92,7 @@
     <t>Actual Result</t>
   </si>
   <si>
-    <t>administrador: digita no campo “Product Number” o numero de produto e no campo “Serial Number”  o numero serial correspondente e pressiona o botao 'Search'</t>
+    <t>administrador: digita no campo “Product Number” o numero de produto e o numero serial correspondente e pressiona o botao 'Search'</t>
   </si>
   <si>
     <t/>
@@ -209,7 +209,7 @@
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="17.578125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="132.3984375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="109.98828125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="21.8984375" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="63.1875" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="30.5234375" customWidth="true" bestFit="true"/>

--- a/output/xlsx/PesquisarExtracao--GT-.xlsx
+++ b/output/xlsx/PesquisarExtracao--GT-.xlsx
@@ -71,7 +71,7 @@
     <t xml:space="preserve">Precondition: </t>
   </si>
   <si>
-    <t>Usuário deve estar logado com perfil de administrador ; Deve existir ao menos uma extracao cadastrada</t>
+    <t>Usuário deve estar logado com perfil de administrador ; Deve existir ao menos uma extração cadastrada</t>
   </si>
   <si>
     <t>#</t>
@@ -92,13 +92,13 @@
     <t>Actual Result</t>
   </si>
   <si>
-    <t>administrador: digita no campo “Product Number” o numero de produto e o numero serial correspondente e pressiona o botao 'Search'</t>
+    <t>administrador: digita no campo “Product Number” o número de produto e o número serial correspondente e pressiona o botão 'Search'</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>SYSTEM exibe tela correspondente a extracao</t>
+    <t>SYSTEM exibe tela correspondente a extração</t>
   </si>
   <si>
     <t xml:space="preserve">Postcondition: </t>
@@ -107,13 +107,13 @@
     <t>TC2</t>
   </si>
   <si>
-    <t>Alternative Flow 1: Product Number ou Serial Number invalidos</t>
-  </si>
-  <si>
-    <t>administrador: digita o product number e/ou numero serial invalidos e pressiona o botao 'Search'</t>
-  </si>
-  <si>
-    <t>SYSTEM exibe mensagem que product number ou serial number sao invalidos</t>
+    <t>Alternative Flow 1: Product Number ou Serial Number inválidos</t>
+  </si>
+  <si>
+    <t>administrador: digita o product number e/ou número serial inválidos e pressiona o botão 'Search'</t>
+  </si>
+  <si>
+    <t>SYSTEM exibe mensagem “No extraction found. Please, insert a Serial Number to search for the last extraction.”</t>
   </si>
 </sst>
 </file>
@@ -211,7 +211,7 @@
     <col min="1" max="1" width="17.578125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="109.98828125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="21.8984375" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="63.1875" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="90.58203125" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="30.5234375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="17.578125" customWidth="true" bestFit="true"/>
   </cols>
